--- a/erp-server/erp-server-wms/src/main/resources/excel/b2bCustomerPackingTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/b2bCustomerPackingTemplate.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22560" windowHeight="11120"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -45,6 +45,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -59,7 +66,19 @@
     </r>
   </si>
   <si>
-    <t>装箱数量</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>装箱数量</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1215,10 +1234,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="3" max="3" width="12.9090909090909" customWidth="1"/>
-    <col min="4" max="5" width="14.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="12.9083333333333" customWidth="1"/>
+    <col min="4" max="5" width="14.6333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1240,7 +1259,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
